--- a/artfynd/A 35595-2025 artfynd.xlsx
+++ b/artfynd/A 35595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184846</v>
       </c>
       <c r="B2" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35595-2025 artfynd.xlsx
+++ b/artfynd/A 35595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184846</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130184854</v>
       </c>
       <c r="B3" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130184844</v>
       </c>
       <c r="B4" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130184845</v>
       </c>
       <c r="B5" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35595-2025 artfynd.xlsx
+++ b/artfynd/A 35595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184846</v>
       </c>
       <c r="B2" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130184854</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130184844</v>
       </c>
       <c r="B4" t="n">
-        <v>83024</v>
+        <v>83027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130184845</v>
       </c>
       <c r="B5" t="n">
-        <v>83024</v>
+        <v>83027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35595-2025 artfynd.xlsx
+++ b/artfynd/A 35595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184846</v>
       </c>
       <c r="B2" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130184854</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130184844</v>
       </c>
       <c r="B4" t="n">
-        <v>83027</v>
+        <v>83053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130184845</v>
       </c>
       <c r="B5" t="n">
-        <v>83027</v>
+        <v>83053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35595-2025 artfynd.xlsx
+++ b/artfynd/A 35595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184846</v>
       </c>
       <c r="B2" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130184844</v>
       </c>
       <c r="B4" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130184845</v>
       </c>
       <c r="B5" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35595-2025 artfynd.xlsx
+++ b/artfynd/A 35595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184846</v>
       </c>
       <c r="B2" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130184844</v>
       </c>
       <c r="B4" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130184845</v>
       </c>
       <c r="B5" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35595-2025 artfynd.xlsx
+++ b/artfynd/A 35595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184846</v>
       </c>
       <c r="B2" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130184854</v>
       </c>
       <c r="B3" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130184844</v>
       </c>
       <c r="B4" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130184845</v>
       </c>
       <c r="B5" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
